--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575768649</v>
+        <v>46157.93120824423</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93120824423</v>
+        <v>46157.93186481341</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186481341</v>
+        <v>46157.93407130138</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407130138</v>
+        <v>46157.93725271991</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725271991</v>
+        <v>46158.28222771705</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222771705</v>
+        <v>46158.29711291704</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29711291704</v>
+        <v>46158.29822834145</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822834145</v>
+        <v>46158.3339376432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339376432</v>
+        <v>46158.36863525923</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Майингаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863525923</v>
+        <v>46158.37294522432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
